--- a/Team10_Chhattisgarh_Source_Inventory_Phase1.xlsx
+++ b/Team10_Chhattisgarh_Source_Inventory_Phase1.xlsx
@@ -747,7 +747,7 @@
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>District and state level aggregate data across four fact areas (procurement, prices, storage, advisories) for paddy and other notified commodities including minor forest produce, collected in five modalities (API and CSV, HTML tables and listings, digital PDF, scanned PDF requiring OCR including Hindi, and voice/audio derived text from the Kisan Call Centre archive), sourced from official channels with full source and date provenance. Crop stages covered: seed and farm planning (variety and seed rate guidance, sowing windows), monitoring and production (procurement), aggregation, storage and logistics (storage), and market and supply chain (prices), with seed and farm planning added through two reference sources in Sheet 2 rather than a new fact table.</t>
+          <t>District and state level aggregate data across four fact areas (procurement, prices, storage, advisories) for paddy and other notified commodities including minor forest produce, collected in four modalities (API and CSV, HTML tables and listings, digital PDF, scanned PDF requiring OCR including Hindi), sourced from official channels with full source and date provenance. The Kisan Call Centre archive adds the project's first voice/audio origin source, but its export is pre transcribed and so is read via the API/CSV path, not a fifth modality. Crop stages covered: seed and farm planning (variety and seed rate guidance, sowing windows), monitoring and production (procurement), aggregation, storage and logistics (storage), and market and supply chain (prices), with seed and farm planning added through two reference sources in Sheet 2 rather than a new fact table.</t>
         </is>
       </c>
       <c r="D19" s="6" t="n"/>
@@ -959,7 +959,7 @@
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>Not started. Begins Phase 2 with sample document collection per source. Modality coverage already confirmed across API and CSV, HTML, digital PDF, scanned Hindi PDF, and voice/audio derived text (Kisan Call Centre archive, read as pre transcribed text; raw recordings would route through the new Whisper based audio_transcribe tool).</t>
+          <t>Not started. Begins Phase 2 with sample document collection per source. Modality coverage already confirmed across the four modalities actually in use: API and CSV, HTML, digital PDF and scanned Hindi PDF. Kisan Call Centre archive text also reads via API/CSV, since it is pre transcribed; a voice_audio value and a Whisper based audio_transcribe tool exist for a future raw-recording source but are not exercised in Phase 1.</t>
         </is>
       </c>
       <c r="D35" s="6" t="n"/>
@@ -3705,7 +3705,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>Advisories. The project's voice/audio modality source; also gives a district level qualitative signal on what farmers were asking about ahead of an advisory or price movement.</t>
+          <t>Advisories. The project's voice/audio origin source; also gives a district level qualitative signal on what farmers were asking about ahead of an advisory or price movement.</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
